--- a/data/nzd0578/nzd0578.xlsx
+++ b/data/nzd0578/nzd0578.xlsx
@@ -6549,7 +6549,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B846"/>
+  <dimension ref="A1:B847"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15012,6 +15012,16 @@
       </c>
       <c r="B846" t="n">
         <v>-0.6</v>
+      </c>
+    </row>
+    <row r="847">
+      <c r="A847" t="inlineStr">
+        <is>
+          <t>2025-11-30 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B847" t="n">
+        <v>-0.73</v>
       </c>
     </row>
   </sheetData>

--- a/data/nzd0578/nzd0578.xlsx
+++ b/data/nzd0578/nzd0578.xlsx
@@ -6549,7 +6549,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B847"/>
+  <dimension ref="A1:B849"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15022,6 +15022,26 @@
       </c>
       <c r="B847" t="n">
         <v>-0.73</v>
+      </c>
+    </row>
+    <row r="848">
+      <c r="A848" t="inlineStr">
+        <is>
+          <t>2025-12-08 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B848" t="n">
+        <v>0.41</v>
+      </c>
+    </row>
+    <row r="849">
+      <c r="A849" t="inlineStr">
+        <is>
+          <t>2025-12-16 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B849" t="n">
+        <v>0.36</v>
       </c>
     </row>
   </sheetData>

--- a/data/nzd0578/nzd0578.xlsx
+++ b/data/nzd0578/nzd0578.xlsx
@@ -6549,7 +6549,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B849"/>
+  <dimension ref="A1:B850"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15042,6 +15042,16 @@
       </c>
       <c r="B849" t="n">
         <v>0.36</v>
+      </c>
+    </row>
+    <row r="850">
+      <c r="A850" t="inlineStr">
+        <is>
+          <t>2026-01-17 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B850" t="n">
+        <v>1.25</v>
       </c>
     </row>
   </sheetData>

--- a/data/nzd0578/nzd0578.xlsx
+++ b/data/nzd0578/nzd0578.xlsx
@@ -6549,7 +6549,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B850"/>
+  <dimension ref="A1:B853"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15052,6 +15052,36 @@
       </c>
       <c r="B850" t="n">
         <v>1.25</v>
+      </c>
+    </row>
+    <row r="851">
+      <c r="A851" t="inlineStr">
+        <is>
+          <t>2026-01-25 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B851" t="n">
+        <v>-0.86</v>
+      </c>
+    </row>
+    <row r="852">
+      <c r="A852" t="inlineStr">
+        <is>
+          <t>2026-02-10 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B852" t="n">
+        <v>-0.59</v>
+      </c>
+    </row>
+    <row r="853">
+      <c r="A853" t="inlineStr">
+        <is>
+          <t>2026-02-18 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B853" t="n">
+        <v>1.71</v>
       </c>
     </row>
   </sheetData>

--- a/data/nzd0578/nzd0578.xlsx
+++ b/data/nzd0578/nzd0578.xlsx
@@ -6549,7 +6549,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B853"/>
+  <dimension ref="A1:B855"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15082,6 +15082,26 @@
       </c>
       <c r="B853" t="n">
         <v>1.71</v>
+      </c>
+    </row>
+    <row r="854">
+      <c r="A854" t="inlineStr">
+        <is>
+          <t>2026-03-06 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B854" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="855">
+      <c r="A855" t="inlineStr">
+        <is>
+          <t>2026-03-22 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B855" t="n">
+        <v>0.67</v>
       </c>
     </row>
   </sheetData>

--- a/data/nzd0578/nzd0578.xlsx
+++ b/data/nzd0578/nzd0578.xlsx
@@ -6549,7 +6549,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B855"/>
+  <dimension ref="A1:B859"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15102,6 +15102,46 @@
       </c>
       <c r="B855" t="n">
         <v>0.67</v>
+      </c>
+    </row>
+    <row r="856">
+      <c r="A856" t="inlineStr">
+        <is>
+          <t>2026-03-30 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B856" t="n">
+        <v>1.06</v>
+      </c>
+    </row>
+    <row r="857">
+      <c r="A857" t="inlineStr">
+        <is>
+          <t>2026-04-07 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B857" t="n">
+        <v>0.02</v>
+      </c>
+    </row>
+    <row r="858">
+      <c r="A858" t="inlineStr">
+        <is>
+          <t>2026-04-15 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B858" t="n">
+        <v>1.21</v>
+      </c>
+    </row>
+    <row r="859">
+      <c r="A859" t="inlineStr">
+        <is>
+          <t>2026-04-23 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B859" t="n">
+        <v>-0.82</v>
       </c>
     </row>
   </sheetData>

--- a/data/nzd0578/nzd0578.xlsx
+++ b/data/nzd0578/nzd0578.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C407"/>
+  <dimension ref="A1:C412"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6533,6 +6533,81 @@
         <v>230.62</v>
       </c>
       <c r="C407" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="408">
+      <c r="A408" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-30 22:13:06+00:00</t>
+        </is>
+      </c>
+      <c r="B408" t="n">
+        <v>230.17</v>
+      </c>
+      <c r="C408" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="409">
+      <c r="A409" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-01 22:06:41+00:00</t>
+        </is>
+      </c>
+      <c r="B409" t="n">
+        <v>230.2</v>
+      </c>
+      <c r="C409" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="410">
+      <c r="A410" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-09 22:06:46+00:00</t>
+        </is>
+      </c>
+      <c r="B410" t="n">
+        <v>228.31</v>
+      </c>
+      <c r="C410" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="411">
+      <c r="A411" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-17 22:06:20+00:00</t>
+        </is>
+      </c>
+      <c r="B411" t="n">
+        <v>229.13</v>
+      </c>
+      <c r="C411" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="412">
+      <c r="A412" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-25 22:06:32+00:00</t>
+        </is>
+      </c>
+      <c r="B412" t="n">
+        <v>227.53</v>
+      </c>
+      <c r="C412" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -6549,7 +6624,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B859"/>
+  <dimension ref="A1:B864"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15142,6 +15217,56 @@
       </c>
       <c r="B859" t="n">
         <v>-0.82</v>
+      </c>
+    </row>
+    <row r="860">
+      <c r="A860" t="inlineStr">
+        <is>
+          <t>2026-04-30 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B860" t="n">
+        <v>1.38</v>
+      </c>
+    </row>
+    <row r="861">
+      <c r="A861" t="inlineStr">
+        <is>
+          <t>2026-05-01 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B861" t="n">
+        <v>1.53</v>
+      </c>
+    </row>
+    <row r="862">
+      <c r="A862" t="inlineStr">
+        <is>
+          <t>2026-05-09 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B862" t="n">
+        <v>-0.73</v>
+      </c>
+    </row>
+    <row r="863">
+      <c r="A863" t="inlineStr">
+        <is>
+          <t>2026-05-17 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B863" t="n">
+        <v>1.81</v>
+      </c>
+    </row>
+    <row r="864">
+      <c r="A864" t="inlineStr">
+        <is>
+          <t>2026-05-25 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B864" t="n">
+        <v>-0.65</v>
       </c>
     </row>
   </sheetData>
@@ -15304,28 +15429,28 @@
         <v>0.2</v>
       </c>
       <c r="I2" t="n">
-        <v>0.2118873161195477</v>
+        <v>0.2130380777819767</v>
       </c>
       <c r="J2" t="n">
-        <v>406</v>
+        <v>411</v>
       </c>
       <c r="K2" t="n">
-        <v>406</v>
+        <v>411</v>
       </c>
       <c r="L2" t="n">
-        <v>0.1380097704326608</v>
+        <v>0.1438078659470065</v>
       </c>
       <c r="M2" t="n">
-        <v>3.348721617901664</v>
+        <v>3.319089872682282</v>
       </c>
       <c r="N2" t="n">
-        <v>16.81465538803049</v>
+        <v>16.62554833951257</v>
       </c>
       <c r="O2" t="n">
-        <v>4.100567690946034</v>
+        <v>4.077443848725887</v>
       </c>
       <c r="P2" t="n">
-        <v>222.9498192221913</v>
+        <v>222.9398287796462</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -15363,7 +15488,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C407"/>
+  <dimension ref="A1:C412"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22285,6 +22410,91 @@
         </is>
       </c>
     </row>
+    <row r="408">
+      <c r="A408" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-30 22:13:06+00:00</t>
+        </is>
+      </c>
+      <c r="B408" t="inlineStr">
+        <is>
+          <t>-41.031557342238905,173.02144794727255</t>
+        </is>
+      </c>
+      <c r="C408" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="409">
+      <c r="A409" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-01 22:06:41+00:00</t>
+        </is>
+      </c>
+      <c r="B409" t="inlineStr">
+        <is>
+          <t>-41.0315573704209,173.02144830220868</t>
+        </is>
+      </c>
+      <c r="C409" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="410">
+      <c r="A410" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-09 22:06:46+00:00</t>
+        </is>
+      </c>
+      <c r="B410" t="inlineStr">
+        <is>
+          <t>-41.03155559495354,173.02142594123367</t>
+        </is>
+      </c>
+      <c r="C410" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="411">
+      <c r="A411" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-17 22:06:20+00:00</t>
+        </is>
+      </c>
+      <c r="B411" t="inlineStr">
+        <is>
+          <t>-41.03155636526265,173.02143564282056</t>
+        </is>
+      </c>
+      <c r="C411" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="412">
+      <c r="A412" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-25 22:06:32+00:00</t>
+        </is>
+      </c>
+      <c r="B412" t="inlineStr">
+        <is>
+          <t>-41.031554862219714,173.0214167128951</t>
+        </is>
+      </c>
+      <c r="C412" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0578/nzd0578.xlsx
+++ b/data/nzd0578/nzd0578.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C412"/>
+  <dimension ref="A1:C415"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6608,6 +6608,51 @@
         <v>227.53</v>
       </c>
       <c r="C412" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="413">
+      <c r="A413" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-02 22:06:19+00:00</t>
+        </is>
+      </c>
+      <c r="B413" t="n">
+        <v>227.65</v>
+      </c>
+      <c r="C413" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="414">
+      <c r="A414" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-09 22:12:05+00:00</t>
+        </is>
+      </c>
+      <c r="B414" t="n">
+        <v>228.26</v>
+      </c>
+      <c r="C414" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="415">
+      <c r="A415" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-10 22:06:30+00:00</t>
+        </is>
+      </c>
+      <c r="B415" t="n">
+        <v>228.86</v>
+      </c>
+      <c r="C415" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -6624,7 +6669,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B864"/>
+  <dimension ref="A1:B867"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15267,6 +15312,36 @@
       </c>
       <c r="B864" t="n">
         <v>-0.65</v>
+      </c>
+    </row>
+    <row r="865">
+      <c r="A865" t="inlineStr">
+        <is>
+          <t>2026-06-02 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B865" t="n">
+        <v>1.03</v>
+      </c>
+    </row>
+    <row r="866">
+      <c r="A866" t="inlineStr">
+        <is>
+          <t>2026-06-09 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B866" t="n">
+        <v>-1.06</v>
+      </c>
+    </row>
+    <row r="867">
+      <c r="A867" t="inlineStr">
+        <is>
+          <t>2026-06-10 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B867" t="n">
+        <v>-0.8100000000000001</v>
       </c>
     </row>
   </sheetData>
@@ -15429,28 +15504,28 @@
         <v>0.2</v>
       </c>
       <c r="I2" t="n">
-        <v>0.2130380777819767</v>
+        <v>0.2123756419729096</v>
       </c>
       <c r="J2" t="n">
-        <v>411</v>
+        <v>414</v>
       </c>
       <c r="K2" t="n">
-        <v>411</v>
+        <v>414</v>
       </c>
       <c r="L2" t="n">
-        <v>0.1438078659470065</v>
+        <v>0.1457307988418743</v>
       </c>
       <c r="M2" t="n">
-        <v>3.319089872682282</v>
+        <v>3.299561699937896</v>
       </c>
       <c r="N2" t="n">
-        <v>16.62554833951257</v>
+        <v>16.50806022232198</v>
       </c>
       <c r="O2" t="n">
-        <v>4.077443848725887</v>
+        <v>4.063011225965537</v>
       </c>
       <c r="P2" t="n">
-        <v>222.9398287796462</v>
+        <v>222.9456060536102</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -15488,7 +15563,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C412"/>
+  <dimension ref="A1:C415"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22495,6 +22570,57 @@
         </is>
       </c>
     </row>
+    <row r="413">
+      <c r="A413" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-02 22:06:19+00:00</t>
+        </is>
+      </c>
+      <c r="B413" t="inlineStr">
+        <is>
+          <t>-41.031554974948044,173.0214181326395</t>
+        </is>
+      </c>
+      <c r="C413" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="414">
+      <c r="A414" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-09 22:12:05+00:00</t>
+        </is>
+      </c>
+      <c r="B414" t="inlineStr">
+        <is>
+          <t>-41.031555547983444,173.0214253496735</t>
+        </is>
+      </c>
+      <c r="C414" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="415">
+      <c r="A415" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-10 22:06:30+00:00</t>
+        </is>
+      </c>
+      <c r="B415" t="inlineStr">
+        <is>
+          <t>-41.03155611162438,173.0214324483956</t>
+        </is>
+      </c>
+      <c r="C415" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
